--- a/data/trans_orig/P70D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de su capacidad laboral actual en 2023</t>
+          <t>Población según su autopercepción de su capacidad laboral actual en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -728,12 +728,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85583</t>
+          <t>82645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39036</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>57058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96077</t>
+          <t>98260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>134260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92252</t>
+          <t>93691</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125214</t>
+          <t>125317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67910</t>
+          <t>67674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87312</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>169083</t>
+          <t>165245</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>206891</t>
+          <t>204377</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>20948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97464</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141587</t>
+          <t>140160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71898</t>
+          <t>71924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>94701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181754</t>
+          <t>181346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225810</t>
+          <t>227219</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>56581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97087</t>
+          <t>96971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46831</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91185</t>
+          <t>92722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134126</t>
+          <t>136529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68430</t>
+          <t>67887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26857</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38311</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>18046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>64966</t>
+          <t>64479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>88348</t>
+          <t>89477</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63373</t>
+          <t>62803</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>144703</t>
+          <t>146186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39999</t>
+          <t>39797</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>34087</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43851</t>
+          <t>42916</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>67746</t>
+          <t>67243</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>15294</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>40753</t>
+          <t>39860</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>64571</t>
+          <t>62563</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15091</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43598</t>
+          <t>46123</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24517</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>143373</t>
+          <t>133737</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>181356</t>
+          <t>174029</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>31972</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>60851</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>193019</t>
+          <t>203061</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>91720</t>
+          <t>92159</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>273132</t>
+          <t>265397</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>75830</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>93260</t>
+          <t>91760</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>66656</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>156135</t>
+          <t>154379</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>48260</t>
+          <t>47914</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>26563</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>22909</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>277</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>32344</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>51709</t>
+          <t>52016</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>26883</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>34510</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>51311</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>72024</t>
+          <t>72514</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>33277</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>50716</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>43958</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>57780</t>
+          <t>57895</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>81678</t>
+          <t>80821</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>105216</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>16528</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>822</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6857,12 +6857,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7225,12 +7225,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7418,12 +7418,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>53762</t>
+          <t>52736</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>75758</t>
+          <t>74310</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>32582</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>91393</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>118416</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>23157</t>
+          <t>24028</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7544,12 +7544,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>38979</t>
+          <t>38970</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>62059</t>
+          <t>62080</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>40133</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -7751,12 +7751,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -7862,12 +7862,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -7973,12 +7973,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>812</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8023,12 +8023,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>918</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>496</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>503</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8321,82 +8321,82 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="S72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T72" s="2" t="inlineStr">
-        <is>
-          <t>2968</t>
-        </is>
-      </c>
-      <c r="U72" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V72" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W72" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -8756,12 +8756,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>87819</t>
+          <t>85256</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>128927</t>
+          <t>127390</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>84263</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>112327</t>
+          <t>113941</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>176420</t>
+          <t>177572</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>229715</t>
+          <t>230430</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>76258</t>
+          <t>76874</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>112746</t>
+          <t>112995</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>71086</t>
+          <t>70916</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>97415</t>
+          <t>97035</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>154048</t>
+          <t>156056</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>200495</t>
+          <t>202147</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>85056</t>
+          <t>85012</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>122327</t>
+          <t>123312</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>89494</t>
+          <t>87990</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>116795</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>181012</t>
+          <t>183959</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>229289</t>
+          <t>233785</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>43128</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>24544</t>
+          <t>26035</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>30792</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>60570</t>
+          <t>59311</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -9200,12 +9200,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>18413</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -9533,12 +9533,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9679,12 +9679,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>72322</t>
+          <t>75886</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>324784</t>
+          <t>322871</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>83248</t>
+          <t>83730</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>112444</t>
+          <t>111117</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>133670</t>
+          <t>133342</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>407684</t>
+          <t>409244</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>129702</t>
+          <t>130212</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>512582</t>
+          <t>508808</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>57600</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>83764</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>201587</t>
+          <t>200859</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>664140</t>
+          <t>661612</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -10316,12 +10316,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>119261</t>
+          <t>120206</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>45157</t>
+          <t>44997</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>70039</t>
+          <t>69237</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10366,12 +10366,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10386,12 +10386,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>57283</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>179681</t>
+          <t>178533</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -10427,12 +10427,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>44654</t>
+          <t>43214</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>67541</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -10538,12 +10538,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>27455</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10719,12 +10719,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>33997</t>
+          <t>33444</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>497</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -10871,12 +10871,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10982,12 +10982,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11067,12 +11067,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11108,12 +11108,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11143,12 +11143,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11178,12 +11178,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11219,12 +11219,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11254,12 +11254,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11289,12 +11289,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11432,12 +11432,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>429231</t>
+          <t>374173</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>720694</t>
+          <t>723172</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11447,12 +11447,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>396944</t>
+          <t>401919</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>538004</t>
+          <t>533742</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>846002</t>
+          <t>829683</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>1199173</t>
+          <t>1195316</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>516881</t>
+          <t>513755</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>1101042</t>
+          <t>1214383</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>348449</t>
+          <t>352638</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>582346</t>
+          <t>574774</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>905732</t>
+          <t>909197</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>1687297</t>
+          <t>1656796</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -11654,12 +11654,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>301033</t>
+          <t>265738</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>530830</t>
+          <t>533171</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>341864</t>
+          <t>348749</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>443784</t>
+          <t>447533</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11724,12 +11724,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>663246</t>
+          <t>676970</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>959748</t>
+          <t>955252</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -11765,12 +11765,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>70868</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>139277</t>
+          <t>141579</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>78721</t>
+          <t>79634</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>115829</t>
+          <t>117285</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -11815,12 +11815,12 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>162013</t>
+          <t>158828</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>245015</t>
+          <t>244146</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -11876,12 +11876,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>31528</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>64796</t>
+          <t>67635</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -11891,49 +11891,49 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>35983</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>26655</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>48219</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>35983</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>25995</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>48662</t>
-        </is>
-      </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="P104" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>64067</t>
+          <t>63569</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>106637</t>
+          <t>108241</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>50331</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>60842</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -12098,12 +12098,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12113,12 +12113,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12168,12 +12168,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12244,12 +12244,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12279,12 +12279,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12294,12 +12294,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -12320,12 +12320,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12355,12 +12355,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
@@ -12405,12 +12405,12 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70D_2023-Provincia-trans_orig.xlsx
@@ -723,102 +723,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5945</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10173</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>14337</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>8901</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>22799</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>6,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4220</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7339</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>9602</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>5469</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>16498</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -834,32 +834,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67797</t>
+          <t>70102</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52678</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82645</t>
+          <t>84344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47468</t>
+          <t>50344</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>40303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57058</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115265</t>
+          <t>120447</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98260</t>
+          <t>103973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134260</t>
+          <t>135880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -945,32 +945,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109120</t>
+          <t>110629</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93691</t>
+          <t>95915</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125317</t>
+          <t>124355</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -980,32 +980,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77767</t>
+          <t>81886</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67674</t>
+          <t>72855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87766</t>
+          <t>92693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>186887</t>
+          <t>192515</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165245</t>
+          <t>175535</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>204377</t>
+          <t>210564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>23037</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>32953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -1167,32 +1167,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>869</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>468</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>121189</t>
+          <t>126966</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100603</t>
+          <t>106762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140160</t>
+          <t>145935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>84188</t>
+          <t>90227</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71924</t>
+          <t>78373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94701</t>
+          <t>103393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>205377</t>
+          <t>217194</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181346</t>
+          <t>193206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227219</t>
+          <t>240667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -2172,32 +2172,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75677</t>
+          <t>77342</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56581</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96971</t>
+          <t>99172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2207,32 +2207,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36650</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>27670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>112328</t>
+          <t>114627</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92722</t>
+          <t>96679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136529</t>
+          <t>139615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -2283,32 +2283,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39710</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2318,32 +2318,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2353,32 +2353,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>51372</t>
+          <t>51993</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67809</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -2394,32 +2394,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2429,32 +2429,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>21273</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2464,32 +2464,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25643</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41805</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2505,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2540,32 +2540,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>693</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>845</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>845</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3241,32 +3241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3399,32 +3399,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>76373</t>
+          <t>78651</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>64479</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89477</t>
+          <t>89789</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>53957</t>
+          <t>54392</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62803</t>
+          <t>63903</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>130330</t>
+          <t>133043</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>116976</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>146186</t>
+          <t>147994</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>20714</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39797</t>
+          <t>39659</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3545,32 +3545,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>33065</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3580,32 +3580,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>54453</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>43183</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>67243</t>
+          <t>67782</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -3621,32 +3621,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>39375</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3656,32 +3656,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29470</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3691,32 +3691,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>51077</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>40176</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>62563</t>
+          <t>66289</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -3732,32 +3732,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3767,32 +3767,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3802,32 +3802,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -3843,17 +3843,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3878,32 +3878,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3913,32 +3913,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3989,32 +3989,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4024,32 +4024,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>645</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>645</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4176,17 +4176,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4246,17 +4246,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -4322,32 +4322,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>818</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4468,17 +4468,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>903</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>903</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4622,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4657,17 +4657,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>43850</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>29613</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>46123</t>
+          <t>65988</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4772,32 +4772,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>63440</t>
+          <t>35401</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>133737</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4807,32 +4807,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>93611</t>
+          <t>79251</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54208</t>
+          <t>60972</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>174029</t>
+          <t>100830</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>45359</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>31972</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>109128</t>
+          <t>45129</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>48316</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>203061</t>
+          <t>57520</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>154486</t>
+          <t>98153</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>92159</t>
+          <t>78972</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>265397</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -4959,32 +4959,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>58655</t>
+          <t>77334</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>74974</t>
+          <t>96336</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4994,32 +4994,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>58017</t>
+          <t>68147</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>53552</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>91760</t>
+          <t>81745</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5029,32 +5029,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>116672</t>
+          <t>145480</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>122140</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>154379</t>
+          <t>170384</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -5070,22 +5070,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>33675</t>
+          <t>37564</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5140,32 +5140,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>32802</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>47914</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -5181,32 +5181,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5216,32 +5216,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5251,32 +5251,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -5292,32 +5292,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>14343</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5362,32 +5362,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5549,32 +5549,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5584,32 +5584,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5960,17 +5960,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>165447</t>
+          <t>209450</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>165447</t>
+          <t>209450</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>165447</t>
+          <t>209450</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5995,17 +5995,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>423280</t>
+          <t>388894</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>423280</t>
+          <t>388894</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>423280</t>
+          <t>388894</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6075,32 +6075,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>26518</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>36618</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6110,32 +6110,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>41677</t>
+          <t>46636</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>36829</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>57400</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -6186,32 +6186,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>34332</t>
+          <t>41553</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>32916</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>51666</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6221,32 +6221,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>30389</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>21254</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>34423</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6256,32 +6256,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>61717</t>
+          <t>71942</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>60123</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>72514</t>
+          <t>84479</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -6297,102 +6297,102 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>33277</t>
+          <t>40734</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>50716</t>
+          <t>59950</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>36,54%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>29,92%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>44,03%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>56004</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>48404</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>63806</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>47,05%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>105751</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>93913</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>119376</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>41,44%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
           <t>36,8%</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>44,39%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>50657</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>43958</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>57895</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>47,47%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>41,19%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>54,25%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>92698</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>80821</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>105216</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>41,95%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -6408,32 +6408,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6443,32 +6443,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6478,32 +6478,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>29171</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -6519,32 +6519,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6554,32 +6554,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6589,32 +6589,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>870</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>106720</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>106720</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>106720</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>255181</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>255181</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>255181</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>64033</t>
+          <t>64072</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>52407</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>74310</t>
+          <t>75445</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>41163</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>33997</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>49226</t>
+          <t>49658</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>104690</t>
+          <t>105235</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>91393</t>
+          <t>91258</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>117981</t>
+          <t>119003</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,26%</t>
         </is>
       </c>
     </row>
@@ -7524,27 +7524,27 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>32107</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>42370</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -7559,32 +7559,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7594,32 +7594,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>49630</t>
+          <t>50198</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>38970</t>
+          <t>39601</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>62080</t>
+          <t>60380</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -7635,32 +7635,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7670,32 +7670,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7705,32 +7705,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>40690</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -7746,32 +7746,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7816,32 +7816,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -7857,32 +7857,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7927,32 +7927,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -7968,32 +7968,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8038,32 +8038,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8149,17 +8149,17 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>872</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8225,32 +8225,32 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>512</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8260,32 +8260,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>557</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>557</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -8636,17 +8636,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8751,32 +8751,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>126294</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>85256</t>
+          <t>103641</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>127390</t>
+          <t>148826</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8786,32 +8786,32 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>97831</t>
+          <t>113854</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>84263</t>
+          <t>99443</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>113941</t>
+          <t>130714</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8821,32 +8821,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>203477</t>
+          <t>240148</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>177572</t>
+          <t>213108</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>230430</t>
+          <t>267805</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -8862,32 +8862,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>110500</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>76874</t>
+          <t>90792</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>112995</t>
+          <t>130699</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -8897,32 +8897,32 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>83518</t>
+          <t>97523</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>70916</t>
+          <t>82823</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>97035</t>
+          <t>113920</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -8932,32 +8932,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>177470</t>
+          <t>208023</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>156056</t>
+          <t>184088</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>202147</t>
+          <t>233223</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -8973,32 +8973,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>103939</t>
+          <t>114940</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>85012</t>
+          <t>96940</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>123312</t>
+          <t>137565</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9008,32 +9008,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>124526</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>87990</t>
+          <t>108184</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>141072</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>206528</t>
+          <t>239466</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>183959</t>
+          <t>213419</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>233785</t>
+          <t>266641</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -9084,32 +9084,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>46646</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9119,32 +9119,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>26035</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9154,32 +9154,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>42618</t>
+          <t>50179</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>30792</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>59311</t>
+          <t>66311</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -9195,32 +9195,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9230,22 +9230,22 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9265,32 +9265,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -9341,32 +9341,32 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9376,32 +9376,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>675</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>703</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -9974,17 +9974,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10009,17 +10009,17 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>307415</t>
+          <t>362993</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>307415</t>
+          <t>362993</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>307415</t>
+          <t>362993</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10044,17 +10044,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>642900</t>
+          <t>751719</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>642900</t>
+          <t>751719</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>642900</t>
+          <t>751719</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>191393</t>
+          <t>221803</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>75886</t>
+          <t>200882</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>322871</t>
+          <t>246319</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>98399</t>
+          <t>116430</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>83730</t>
+          <t>100896</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>111117</t>
+          <t>131363</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10159,32 +10159,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>289792</t>
+          <t>338233</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>133342</t>
+          <t>308124</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>409244</t>
+          <t>365111</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -10200,32 +10200,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>328681</t>
+          <t>101057</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>130212</t>
+          <t>80685</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>508808</t>
+          <t>121804</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>69463</t>
+          <t>77315</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>57600</t>
+          <t>64908</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>83764</t>
+          <t>93754</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10270,32 +10270,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>398144</t>
+          <t>178372</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>200859</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>661612</t>
+          <t>201390</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -10311,32 +10311,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>67797</t>
+          <t>78216</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>60863</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>120206</t>
+          <t>96582</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10346,32 +10346,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>56434</t>
+          <t>67755</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>44997</t>
+          <t>55095</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>69237</t>
+          <t>81811</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10381,32 +10381,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>124231</t>
+          <t>145971</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>124929</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>178533</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -10422,32 +10422,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>34009</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>23806</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10457,32 +10457,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>33337</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10492,32 +10492,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>44770</t>
+          <t>58257</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>44063</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>67933</t>
+          <t>75513</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -10533,32 +10533,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10568,32 +10568,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10603,32 +10603,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>40321</t>
+          <t>42610</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10679,32 +10679,32 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>32654</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10714,32 +10714,32 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>33444</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -10765,12 +10765,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10790,32 +10790,32 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10825,32 +10825,32 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -11312,17 +11312,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>627126</t>
+          <t>453632</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>627126</t>
+          <t>453632</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>627126</t>
+          <t>453632</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11347,17 +11347,17 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -11382,17 +11382,17 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>899137</t>
+          <t>766776</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>899137</t>
+          <t>766776</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>899137</t>
+          <t>766776</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -11427,32 +11427,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>617434</t>
+          <t>696546</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>374173</t>
+          <t>649340</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>723172</t>
+          <t>745352</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>461122</t>
+          <t>477530</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>401919</t>
+          <t>445435</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>533742</t>
+          <t>512618</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>1078556</t>
+          <t>1174076</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>829683</t>
+          <t>1115583</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>1195316</t>
+          <t>1234637</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -11538,32 +11538,32 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>707585</t>
+          <t>515172</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>513755</t>
+          <t>474516</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>1214383</t>
+          <t>558838</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11573,32 +11573,32 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>416076</t>
+          <t>381042</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>352638</t>
+          <t>352488</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>574774</t>
+          <t>409963</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11608,32 +11608,32 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>1123662</t>
+          <t>896215</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>909197</t>
+          <t>843995</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>1656796</t>
+          <t>954988</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>455001</t>
+          <t>503228</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>265738</t>
+          <t>462067</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>533171</t>
+          <t>552410</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>405010</t>
+          <t>459564</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>348749</t>
+          <t>428191</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>447533</t>
+          <t>495089</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>860011</t>
+          <t>962792</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>676970</t>
+          <t>907123</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>955252</t>
+          <t>1015872</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -11760,32 +11760,32 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>110058</t>
+          <t>134548</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>111472</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>141579</t>
+          <t>164383</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11795,32 +11795,32 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>97655</t>
+          <t>106840</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>79634</t>
+          <t>89216</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>117285</t>
+          <t>126154</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -11830,32 +11830,32 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>207713</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>158828</t>
+          <t>212052</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>244146</t>
+          <t>271739</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -11871,32 +11871,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>40569</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>67635</t>
+          <t>72150</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>35983</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>54106</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -11941,32 +11941,32 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>84909</t>
+          <t>94702</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>63569</t>
+          <t>76141</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>108241</t>
+          <t>117486</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -11982,32 +11982,32 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>40572</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12052,32 +12052,32 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>56342</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -12093,32 +12093,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12128,67 +12128,67 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>11452</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>18737</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="P106" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q106" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R106" s="2" t="inlineStr">
-        <is>
-          <t>11053</t>
-        </is>
-      </c>
-      <c r="S106" s="2" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="T106" s="2" t="inlineStr">
-        <is>
-          <t>18776</t>
-        </is>
-      </c>
-      <c r="U106" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V106" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -12204,32 +12204,32 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12239,67 +12239,67 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>17599</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="P107" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R107" s="2" t="inlineStr">
-        <is>
-          <t>9163</t>
-        </is>
-      </c>
-      <c r="S107" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="T107" s="2" t="inlineStr">
-        <is>
-          <t>15830</t>
-        </is>
-      </c>
-      <c r="U107" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V107" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -12350,17 +12350,17 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -12370,39 +12370,39 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>5076</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>2475</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="P108" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R108" s="2" t="inlineStr">
-        <is>
-          <t>5041</t>
-        </is>
-      </c>
-      <c r="S108" s="2" t="inlineStr">
-        <is>
-          <t>2264</t>
-        </is>
-      </c>
-      <c r="T108" s="2" t="inlineStr">
-        <is>
-          <t>9151</t>
-        </is>
-      </c>
-      <c r="U108" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -12426,17 +12426,17 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12461,17 +12461,17 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12496,17 +12496,17 @@
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -12537,32 +12537,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12607,17 +12607,17 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -12650,17 +12650,17 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -12685,17 +12685,17 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -12720,17 +12720,17 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
